--- a/backend_api/surveyors.xlsx
+++ b/backend_api/surveyors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1B9C94-31C7-4ACC-A098-1396DFB50528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD01ADA-D527-45EE-BA1B-5A77BEF21C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57CEFE05-DE23-40EC-B97D-190EF49C4C12}"/>
+    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{57CEFE05-DE23-40EC-B97D-190EF49C4C12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -128,133 +128,58 @@
     <t>puerto</t>
   </si>
   <si>
-    <t>Costaricense</t>
-  </si>
-  <si>
     <t>Casado</t>
   </si>
   <si>
     <t>Masculino</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>MEXICO</t>
-  </si>
-  <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
     <t>Semanal</t>
   </si>
   <si>
-    <t>Mexicano</t>
-  </si>
-  <si>
     <t>Por Horas</t>
   </si>
   <si>
-    <t>DRAFT SURVEY</t>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Mendez</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>10ma. Calle Barrio Peñate, Condominio El Paraiso</t>
+  </si>
+  <si>
+    <t>luuu1.mendez@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAC San Jose </t>
+  </si>
+  <si>
+    <t>Avenida 30 de Junio, Puerto San Jose, Escuentla</t>
+  </si>
+  <si>
+    <t>GTQ</t>
+  </si>
+  <si>
+    <t>Guatemalteco</t>
+  </si>
+  <si>
+    <t>Escuintla</t>
+  </si>
+  <si>
+    <t>Puerto San Jose</t>
+  </si>
+  <si>
+    <t>MSL-0018-S</t>
   </si>
   <si>
     <t>ON HIRE BUNKER SURVEY</t>
-  </si>
-  <si>
-    <t>OFF HIRE BUNKER SURVEY</t>
-  </si>
-  <si>
-    <t>BCMRMXMMPYM</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t>Quintero Sosa</t>
-  </si>
-  <si>
-    <t>Av Palmas del Sol No 102 Int. 12D, Col. Solares, Manzanillo, Colima Mexico C.P. 28219</t>
-  </si>
-  <si>
-    <t>marinesurveyor.mzo@gmail.com</t>
-  </si>
-  <si>
-    <t>BBVA México, S.A</t>
-  </si>
-  <si>
-    <t>Av. Paseo de la Reforma 510, Col Juárez, CP 06600, alcaldía Cuauhtémoc, Ciudad de México.</t>
-  </si>
-  <si>
-    <t>012095004562991135</t>
-  </si>
-  <si>
-    <t>COLIMA</t>
-  </si>
-  <si>
-    <t>MANZANILLO</t>
-  </si>
-  <si>
-    <t>BQS BUNKER QUANTITY SURVEY</t>
-  </si>
-  <si>
-    <t>Patricia</t>
-  </si>
-  <si>
-    <t>Omier</t>
-  </si>
-  <si>
-    <t>Limon</t>
-  </si>
-  <si>
-    <t>BCR</t>
-  </si>
-  <si>
-    <t>BCR Avenida Central San jose</t>
-  </si>
-  <si>
-    <t>CR56015202001359844226</t>
-  </si>
-  <si>
-    <t>Femenino</t>
-  </si>
-  <si>
-    <t>LOGISTICS SUPERVISON</t>
-  </si>
-  <si>
-    <t>Magally</t>
-  </si>
-  <si>
-    <t>Barquero</t>
-  </si>
-  <si>
-    <t>Puntarenas</t>
-  </si>
-  <si>
-    <t>Nacional</t>
-  </si>
-  <si>
-    <t>CR80015100320010911006</t>
-  </si>
-  <si>
-    <t>MSL-0011-S</t>
-  </si>
-  <si>
-    <t>MSL-0012-S</t>
-  </si>
-  <si>
-    <t>MSL-0013-S</t>
-  </si>
-  <si>
-    <t>MSL-0014-S</t>
-  </si>
-  <si>
-    <t>MSL-0015-S</t>
-  </si>
-  <si>
-    <t>MSL-0016-S</t>
   </si>
 </sst>
 </file>
@@ -299,10 +224,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -638,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7E6F81-3220-40FC-B0E6-256121CC6AD4}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -766,544 +690,90 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2">
+        <v>47560885</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2">
+        <v>974289910</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2">
+        <v>502</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2">
-        <v>13141612391</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="V2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" t="s">
+        <v>34</v>
+      </c>
+      <c r="X2" t="s">
         <v>47</v>
       </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="Y2">
+        <v>350</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="s">
         <v>32</v>
       </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2">
-        <v>52</v>
-      </c>
-      <c r="T2" t="s">
-        <v>51</v>
-      </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W2" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y2">
-        <v>400</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>34</v>
-      </c>
       <c r="AB2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3">
-        <v>13141612391</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" t="s">
         <v>32</v>
-      </c>
-      <c r="R3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3">
-        <v>52</v>
-      </c>
-      <c r="T3" t="s">
-        <v>51</v>
-      </c>
-      <c r="U3" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" t="s">
-        <v>52</v>
-      </c>
-      <c r="W3" t="s">
-        <v>39</v>
-      </c>
-      <c r="X3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y3">
-        <v>750</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4">
-        <v>13141612391</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>38</v>
-      </c>
-      <c r="S4">
-        <v>52</v>
-      </c>
-      <c r="T4" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" t="s">
-        <v>52</v>
-      </c>
-      <c r="W4" t="s">
-        <v>39</v>
-      </c>
-      <c r="X4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y4">
-        <v>750</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5">
-        <v>13141612391</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5">
-        <v>52</v>
-      </c>
-      <c r="T5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U5" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" t="s">
-        <v>52</v>
-      </c>
-      <c r="W5" t="s">
-        <v>39</v>
-      </c>
-      <c r="X5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y5">
-        <v>450</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>62107301</v>
-      </c>
-      <c r="H6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>60</v>
-      </c>
-      <c r="R6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S6">
-        <v>506</v>
-      </c>
-      <c r="T6" t="s">
-        <v>56</v>
-      </c>
-      <c r="U6" t="s">
-        <v>56</v>
-      </c>
-      <c r="V6" t="s">
-        <v>56</v>
-      </c>
-      <c r="W6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y6">
-        <v>6</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7">
-        <v>71090987</v>
-      </c>
-      <c r="H7" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="P7" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>60</v>
-      </c>
-      <c r="R7" t="s">
-        <v>30</v>
-      </c>
-      <c r="S7">
-        <v>506</v>
-      </c>
-      <c r="T7" t="s">
-        <v>64</v>
-      </c>
-      <c r="U7" t="s">
-        <v>64</v>
-      </c>
-      <c r="V7" t="s">
-        <v>64</v>
-      </c>
-      <c r="W7" t="s">
-        <v>39</v>
-      </c>
-      <c r="X7" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y7">
-        <v>6</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{6E02B29D-E684-47D8-9F9B-17C025BA0B6C}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{711C7A66-9EA8-4253-96EE-90B0BB3831C7}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{84FE6273-77E8-450E-BA8A-176DA6AE296A}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{071D304D-1134-4A65-8687-0452ED3D0F8A}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{0B959325-BCA1-44C7-BB9B-C56663960A32}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend_api/surveyors.xlsx
+++ b/backend_api/surveyors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD01ADA-D527-45EE-BA1B-5A77BEF21C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C624A3-8F98-435F-ABBE-8C6BA6D82364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{57CEFE05-DE23-40EC-B97D-190EF49C4C12}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
   <si>
     <t>id</t>
   </si>
@@ -128,9 +128,6 @@
     <t>puerto</t>
   </si>
   <si>
-    <t>Casado</t>
-  </si>
-  <si>
     <t>Masculino</t>
   </si>
   <si>
@@ -143,43 +140,58 @@
     <t>Por Horas</t>
   </si>
   <si>
-    <t>Luis</t>
-  </si>
-  <si>
-    <t>Mendez</t>
-  </si>
-  <si>
-    <t>Guatemala</t>
-  </si>
-  <si>
-    <t>10ma. Calle Barrio Peñate, Condominio El Paraiso</t>
-  </si>
-  <si>
-    <t>luuu1.mendez@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAC San Jose </t>
-  </si>
-  <si>
-    <t>Avenida 30 de Junio, Puerto San Jose, Escuentla</t>
-  </si>
-  <si>
-    <t>GTQ</t>
-  </si>
-  <si>
-    <t>Guatemalteco</t>
-  </si>
-  <si>
-    <t>Escuintla</t>
-  </si>
-  <si>
-    <t>Puerto San Jose</t>
-  </si>
-  <si>
-    <t>MSL-0018-S</t>
-  </si>
-  <si>
     <t>ON HIRE BUNKER SURVEY</t>
+  </si>
+  <si>
+    <t>Dante Waldermar</t>
+  </si>
+  <si>
+    <t>Rodriguez Gonzales</t>
+  </si>
+  <si>
+    <t>MSL-0019-S</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Ruta nacional 240 a 50mts norte hotel raya bonita</t>
+  </si>
+  <si>
+    <t>dante_86@gmail.com</t>
+  </si>
+  <si>
+    <t>Banco Nacional</t>
+  </si>
+  <si>
+    <t>Avenida 2, Boulevar</t>
+  </si>
+  <si>
+    <t>CR89015113220020013552</t>
+  </si>
+  <si>
+    <t>Union libre</t>
+  </si>
+  <si>
+    <t>Costaricense</t>
+  </si>
+  <si>
+    <t>Limon</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>MSL-0020-S</t>
+  </si>
+  <si>
+    <t>MSL-0021-S</t>
+  </si>
+  <si>
+    <t>DRAFT SURVEY</t>
+  </si>
+  <si>
+    <t>OFF HIRE BUNKER SURVEY</t>
   </si>
 </sst>
 </file>
@@ -562,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7E6F81-3220-40FC-B0E6-256121CC6AD4}">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -690,10 +702,10 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
@@ -702,78 +714,264 @@
         <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>47560885</v>
+        <v>87014828</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2">
+        <v>506</v>
+      </c>
+      <c r="T2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2">
-        <v>974289910</v>
-      </c>
-      <c r="P2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2">
-        <v>502</v>
-      </c>
-      <c r="T2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" t="s">
-        <v>44</v>
-      </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>34</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2">
+        <v>300</v>
+      </c>
+      <c r="Z2" t="s">
         <v>47</v>
       </c>
-      <c r="Y2">
-        <v>350</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>42</v>
-      </c>
       <c r="AA2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AB2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3">
+        <v>87014828</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
         <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3">
+        <v>506</v>
+      </c>
+      <c r="T3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y3">
+        <v>300</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>87014828</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4">
+        <v>506</v>
+      </c>
+      <c r="T4" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4">
+        <v>400</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{0B959325-BCA1-44C7-BB9B-C56663960A32}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{1F47A6F1-2990-4772-BF03-AACBCCFDB082}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{D7CA459D-8A93-4B79-AB33-5B20AA7B77E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend_api/surveyors.xlsx
+++ b/backend_api/surveyors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C624A3-8F98-435F-ABBE-8C6BA6D82364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18E83D8-91E4-4EF7-A982-02AE77C9B505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{57CEFE05-DE23-40EC-B97D-190EF49C4C12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57CEFE05-DE23-40EC-B97D-190EF49C4C12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -143,55 +143,109 @@
     <t>ON HIRE BUNKER SURVEY</t>
   </si>
   <si>
-    <t>Dante Waldermar</t>
-  </si>
-  <si>
-    <t>Rodriguez Gonzales</t>
-  </si>
-  <si>
-    <t>MSL-0019-S</t>
-  </si>
-  <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
-    <t>Ruta nacional 240 a 50mts norte hotel raya bonita</t>
-  </si>
-  <si>
-    <t>dante_86@gmail.com</t>
-  </si>
-  <si>
-    <t>Banco Nacional</t>
-  </si>
-  <si>
-    <t>Avenida 2, Boulevar</t>
-  </si>
-  <si>
-    <t>CR89015113220020013552</t>
-  </si>
-  <si>
-    <t>Union libre</t>
-  </si>
-  <si>
-    <t>Costaricense</t>
-  </si>
-  <si>
-    <t>Limon</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
-    <t>MSL-0020-S</t>
-  </si>
-  <si>
-    <t>MSL-0021-S</t>
-  </si>
-  <si>
     <t>DRAFT SURVEY</t>
   </si>
   <si>
     <t>OFF HIRE BUNKER SURVEY</t>
+  </si>
+  <si>
+    <t>MSL-0022-S</t>
+  </si>
+  <si>
+    <t>Pedro José</t>
+  </si>
+  <si>
+    <t>Vallecillos Montoya</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Costado Sur de la Policía Nacional</t>
+  </si>
+  <si>
+    <t>petervallecillo1961@gmail.com</t>
+  </si>
+  <si>
+    <t>Lasife</t>
+  </si>
+  <si>
+    <t>km 5 1/2 carretera a Masaya</t>
+  </si>
+  <si>
+    <t>NI69BCCE00000000000109270842</t>
+  </si>
+  <si>
+    <t>BCCENIMA</t>
+  </si>
+  <si>
+    <t>Casado</t>
+  </si>
+  <si>
+    <t>Nicaraguense</t>
+  </si>
+  <si>
+    <t>Corinto</t>
+  </si>
+  <si>
+    <t>BUNKER SURVEY</t>
+  </si>
+  <si>
+    <t>CARGO CONDITION</t>
+  </si>
+  <si>
+    <t>CARGO DISCHARGE SUPERVISION</t>
+  </si>
+  <si>
+    <t>ON HIRE BUNKER &amp; CONDITION SURVEY</t>
+  </si>
+  <si>
+    <t>OFF HIRE BUNKER &amp; CONDITION SURVEY</t>
+  </si>
+  <si>
+    <t>Port Captancy</t>
+  </si>
+  <si>
+    <t>BQS BUNKER QUANTITY SURVEY</t>
+  </si>
+  <si>
+    <t>SPOT BUNKER SURVEY</t>
+  </si>
+  <si>
+    <t>MSL-0023-S</t>
+  </si>
+  <si>
+    <t>MSL-0024-S</t>
+  </si>
+  <si>
+    <t>MSL-0025-S</t>
+  </si>
+  <si>
+    <t>MSL-0026-S</t>
+  </si>
+  <si>
+    <t>MSL-0027-S</t>
+  </si>
+  <si>
+    <t>MSL-0028-S</t>
+  </si>
+  <si>
+    <t>MSL-0029-S</t>
+  </si>
+  <si>
+    <t>MSL-0030-S</t>
+  </si>
+  <si>
+    <t>MSL-0031-S</t>
+  </si>
+  <si>
+    <t>MSL-0032-S</t>
+  </si>
+  <si>
+    <t>MSL-0033-S</t>
   </si>
 </sst>
 </file>
@@ -574,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7E6F81-3220-40FC-B0E6-256121CC6AD4}">
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -702,64 +756,64 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>87014828</v>
+        <v>57777366</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="s">
         <v>30</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="V2" t="s">
         <v>31</v>
@@ -768,13 +822,13 @@
         <v>33</v>
       </c>
       <c r="X2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y2">
         <v>300</v>
       </c>
       <c r="Z2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="AA2" t="s">
         <v>31</v>
@@ -791,64 +845,64 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>87014828</v>
+        <v>57777366</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
         <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q3" t="s">
         <v>30</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S3">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="V3" t="s">
         <v>31</v>
@@ -863,7 +917,7 @@
         <v>300</v>
       </c>
       <c r="Z3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="AA3" t="s">
         <v>31</v>
@@ -880,64 +934,64 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G4">
-        <v>87014828</v>
+        <v>57777366</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
         <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q4" t="s">
         <v>30</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="S4">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="V4" t="s">
         <v>31</v>
@@ -946,32 +1000,842 @@
         <v>33</v>
       </c>
       <c r="X4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y4">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5">
+        <v>57777366</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
         <v>47</v>
       </c>
-      <c r="AA4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5">
+        <v>505</v>
+      </c>
+      <c r="T5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y5">
+        <v>300</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>57777366</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6">
+        <v>505</v>
+      </c>
+      <c r="T6" t="s">
+        <v>50</v>
+      </c>
+      <c r="U6" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" t="s">
+        <v>33</v>
+      </c>
+      <c r="X6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y6">
+        <v>300</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>57777366</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" t="s">
+        <v>49</v>
+      </c>
+      <c r="S7">
+        <v>505</v>
+      </c>
+      <c r="T7" t="s">
+        <v>50</v>
+      </c>
+      <c r="U7" t="s">
+        <v>50</v>
+      </c>
+      <c r="V7" t="s">
+        <v>31</v>
+      </c>
+      <c r="W7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7">
+        <v>300</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>57777366</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" t="s">
+        <v>49</v>
+      </c>
+      <c r="S8">
+        <v>505</v>
+      </c>
+      <c r="T8" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" t="s">
+        <v>50</v>
+      </c>
+      <c r="V8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" t="s">
+        <v>33</v>
+      </c>
+      <c r="X8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y8">
+        <v>300</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9">
+        <v>57777366</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9">
+        <v>505</v>
+      </c>
+      <c r="T9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" t="s">
+        <v>50</v>
+      </c>
+      <c r="V9" t="s">
+        <v>31</v>
+      </c>
+      <c r="W9" t="s">
+        <v>33</v>
+      </c>
+      <c r="X9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y9">
+        <v>300</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>57777366</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" t="s">
+        <v>49</v>
+      </c>
+      <c r="S10">
+        <v>505</v>
+      </c>
+      <c r="T10" t="s">
+        <v>50</v>
+      </c>
+      <c r="U10" t="s">
+        <v>50</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s">
+        <v>33</v>
+      </c>
+      <c r="X10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y10">
+        <v>300</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11">
+        <v>57777366</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11">
+        <v>505</v>
+      </c>
+      <c r="T11" t="s">
+        <v>50</v>
+      </c>
+      <c r="U11" t="s">
+        <v>50</v>
+      </c>
+      <c r="V11" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" t="s">
+        <v>33</v>
+      </c>
+      <c r="X11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y11">
+        <v>300</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>57777366</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" t="s">
+        <v>49</v>
+      </c>
+      <c r="S12">
+        <v>505</v>
+      </c>
+      <c r="T12" t="s">
+        <v>50</v>
+      </c>
+      <c r="U12" t="s">
+        <v>50</v>
+      </c>
+      <c r="V12" t="s">
+        <v>31</v>
+      </c>
+      <c r="W12" t="s">
+        <v>33</v>
+      </c>
+      <c r="X12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y12">
+        <v>300</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <v>57777366</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>30</v>
+      </c>
+      <c r="R13" t="s">
+        <v>49</v>
+      </c>
+      <c r="S13">
+        <v>505</v>
+      </c>
+      <c r="T13" t="s">
+        <v>50</v>
+      </c>
+      <c r="U13" t="s">
+        <v>50</v>
+      </c>
+      <c r="V13" t="s">
+        <v>31</v>
+      </c>
+      <c r="W13" t="s">
+        <v>33</v>
+      </c>
+      <c r="X13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y13">
+        <v>300</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{0B959325-BCA1-44C7-BB9B-C56663960A32}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{1F47A6F1-2990-4772-BF03-AACBCCFDB082}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{D7CA459D-8A93-4B79-AB33-5B20AA7B77E2}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{D7CA459D-8A93-4B79-AB33-5B20AA7B77E2}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{4EB393FB-7142-4B56-96EB-7138F1C35ECA}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{FBB7E182-7EC4-4D42-A29D-E03360F760C3}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{7C2FF0E8-B6DB-4776-95B9-A6AF92E84319}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{6ED0D6DE-4F7E-4F52-A82E-CB10A06CFF31}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{F45788DD-D174-4B6F-BC98-D50D90DC569F}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{8D17EB4B-EC72-459A-A6B2-351742F25E4D}"/>
+    <hyperlink ref="H9" r:id="rId8" xr:uid="{28CB722F-4007-48A7-AB58-F694A2990E2E}"/>
+    <hyperlink ref="H10" r:id="rId9" xr:uid="{D92991A2-79C7-47FA-AEA4-C564DC70DEC6}"/>
+    <hyperlink ref="H11" r:id="rId10" xr:uid="{655F119F-A636-45AB-920A-A45A48084412}"/>
+    <hyperlink ref="H12" r:id="rId11" xr:uid="{BBD0C27F-8483-4D5B-A64B-18F53024DAAD}"/>
+    <hyperlink ref="H13" r:id="rId12" xr:uid="{8CC5F86B-669A-4426-AA05-8EF0B68541CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
